--- a/R_analysis/output/supplementary/Tabela_Supl_Joinpoint_UF.xlsx
+++ b/R_analysis/output/supplementary/Tabela_Supl_Joinpoint_UF.xlsx
@@ -419,7 +419,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B2">
@@ -456,7 +456,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B3">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B4">
@@ -530,7 +530,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B5">
@@ -564,7 +564,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B6">
@@ -601,7 +601,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B7">
@@ -638,7 +638,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B8">
@@ -675,7 +675,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B9">
@@ -712,7 +712,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B10">
@@ -746,7 +746,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AC — Gestacional</t>
+          <t>AC — Gestational</t>
         </is>
       </c>
       <c r="B11">
@@ -783,7 +783,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AC — Gestacional</t>
+          <t>AC — Gestational</t>
         </is>
       </c>
       <c r="B12">
@@ -820,7 +820,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AC — Gestacional</t>
+          <t>AC — Gestational</t>
         </is>
       </c>
       <c r="B13">
@@ -854,7 +854,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AC — Congênita</t>
+          <t>AC — Congenital</t>
         </is>
       </c>
       <c r="B14">
@@ -891,7 +891,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AC — Congênita</t>
+          <t>AC — Congenital</t>
         </is>
       </c>
       <c r="B15">
@@ -928,7 +928,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AC — Congênita</t>
+          <t>AC — Congenital</t>
         </is>
       </c>
       <c r="B16">
@@ -962,7 +962,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AM — Gestacional</t>
+          <t>AM — Gestational</t>
         </is>
       </c>
       <c r="B17">
@@ -999,7 +999,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AM — Gestacional</t>
+          <t>AM — Gestational</t>
         </is>
       </c>
       <c r="B18">
@@ -1036,7 +1036,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AM — Gestacional</t>
+          <t>AM — Gestational</t>
         </is>
       </c>
       <c r="B19">
@@ -1070,7 +1070,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B20">
@@ -1107,7 +1107,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B21">
@@ -1144,7 +1144,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B22">
@@ -1181,7 +1181,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B23">
@@ -1218,7 +1218,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B24">
@@ -1252,7 +1252,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RR — Gestacional</t>
+          <t>RR — Gestational</t>
         </is>
       </c>
       <c r="B25">
@@ -1289,7 +1289,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RR — Gestacional</t>
+          <t>RR — Gestational</t>
         </is>
       </c>
       <c r="B26">
@@ -1326,7 +1326,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RR — Gestacional</t>
+          <t>RR — Gestational</t>
         </is>
       </c>
       <c r="B27">
@@ -1360,7 +1360,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B28">
@@ -1397,7 +1397,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B29">
@@ -1434,7 +1434,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B30">
@@ -1471,7 +1471,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B31">
@@ -1505,7 +1505,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PA — Gestacional</t>
+          <t>PA — Gestational</t>
         </is>
       </c>
       <c r="B32">
@@ -1542,7 +1542,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PA — Congênita</t>
+          <t>PA — Congenital</t>
         </is>
       </c>
       <c r="B33">
@@ -1579,7 +1579,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PA — Congênita</t>
+          <t>PA — Congenital</t>
         </is>
       </c>
       <c r="B34">
@@ -1613,7 +1613,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AP — Gestacional</t>
+          <t>AP — Gestational</t>
         </is>
       </c>
       <c r="B35">
@@ -1650,7 +1650,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AP — Gestacional</t>
+          <t>AP — Gestational</t>
         </is>
       </c>
       <c r="B36">
@@ -1684,7 +1684,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AP — Congênita</t>
+          <t>AP — Congenital</t>
         </is>
       </c>
       <c r="B37">
@@ -1721,7 +1721,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AP — Congênita</t>
+          <t>AP — Congenital</t>
         </is>
       </c>
       <c r="B38">
@@ -1758,7 +1758,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AP — Congênita</t>
+          <t>AP — Congenital</t>
         </is>
       </c>
       <c r="B39">
@@ -1792,7 +1792,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B40">
@@ -1829,7 +1829,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B41">
@@ -1866,7 +1866,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B42">
@@ -1903,7 +1903,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B43">
@@ -1940,7 +1940,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B44">
@@ -1974,7 +1974,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B45">
@@ -2011,7 +2011,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B46">
@@ -2048,7 +2048,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B47">
@@ -2085,7 +2085,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B48">
@@ -2119,7 +2119,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MA — Gestacional</t>
+          <t>MA — Gestational</t>
         </is>
       </c>
       <c r="B49">
@@ -2156,7 +2156,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MA — Gestacional</t>
+          <t>MA — Gestational</t>
         </is>
       </c>
       <c r="B50">
@@ -2193,7 +2193,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MA — Gestacional</t>
+          <t>MA — Gestational</t>
         </is>
       </c>
       <c r="B51">
@@ -2227,7 +2227,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MA — Congênita</t>
+          <t>MA — Congenital</t>
         </is>
       </c>
       <c r="B52">
@@ -2264,7 +2264,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MA — Congênita</t>
+          <t>MA — Congenital</t>
         </is>
       </c>
       <c r="B53">
@@ -2301,7 +2301,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MA — Congênita</t>
+          <t>MA — Congenital</t>
         </is>
       </c>
       <c r="B54">
@@ -2335,7 +2335,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B55">
@@ -2372,7 +2372,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B56">
@@ -2409,7 +2409,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B57">
@@ -2446,7 +2446,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B58">
@@ -2483,7 +2483,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B59">
@@ -2517,7 +2517,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PI — Congênita</t>
+          <t>PI — Congenital</t>
         </is>
       </c>
       <c r="B60">
@@ -2554,7 +2554,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PI — Congênita</t>
+          <t>PI — Congenital</t>
         </is>
       </c>
       <c r="B61">
@@ -2591,7 +2591,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PI — Congênita</t>
+          <t>PI — Congenital</t>
         </is>
       </c>
       <c r="B62">
@@ -2625,7 +2625,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CE — Gestacional</t>
+          <t>CE — Gestational</t>
         </is>
       </c>
       <c r="B63">
@@ -2662,7 +2662,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CE — Congênita</t>
+          <t>CE — Congenital</t>
         </is>
       </c>
       <c r="B64">
@@ -2699,7 +2699,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CE — Congênita</t>
+          <t>CE — Congenital</t>
         </is>
       </c>
       <c r="B65">
@@ -2733,7 +2733,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RN — Gestacional</t>
+          <t>RN — Gestational</t>
         </is>
       </c>
       <c r="B66">
@@ -2770,7 +2770,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RN — Gestacional</t>
+          <t>RN — Gestational</t>
         </is>
       </c>
       <c r="B67">
@@ -2807,7 +2807,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RN — Gestacional</t>
+          <t>RN — Gestational</t>
         </is>
       </c>
       <c r="B68">
@@ -2841,7 +2841,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RN — Congênita</t>
+          <t>RN — Congenital</t>
         </is>
       </c>
       <c r="B69">
@@ -2878,7 +2878,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RN — Congênita</t>
+          <t>RN — Congenital</t>
         </is>
       </c>
       <c r="B70">
@@ -2912,7 +2912,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B71">
@@ -2949,7 +2949,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B72">
@@ -2986,7 +2986,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B73">
@@ -3023,7 +3023,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B74">
@@ -3057,7 +3057,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PB — Congênita</t>
+          <t>PB — Congenital</t>
         </is>
       </c>
       <c r="B75">
@@ -3091,7 +3091,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B76">
@@ -3128,7 +3128,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B77">
@@ -3165,7 +3165,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B78">
@@ -3202,7 +3202,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B79">
@@ -3236,7 +3236,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B80">
@@ -3273,7 +3273,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B81">
@@ -3310,7 +3310,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B82">
@@ -3347,7 +3347,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B83">
@@ -3384,7 +3384,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B84">
@@ -3418,7 +3418,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AL — Gestacional</t>
+          <t>AL — Gestational</t>
         </is>
       </c>
       <c r="B85">
@@ -3455,7 +3455,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AL — Gestacional</t>
+          <t>AL — Gestational</t>
         </is>
       </c>
       <c r="B86">
@@ -3492,7 +3492,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AL — Gestacional</t>
+          <t>AL — Gestational</t>
         </is>
       </c>
       <c r="B87">
@@ -3526,7 +3526,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AL — Congênita</t>
+          <t>AL — Congenital</t>
         </is>
       </c>
       <c r="B88">
@@ -3563,7 +3563,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AL — Congênita</t>
+          <t>AL — Congenital</t>
         </is>
       </c>
       <c r="B89">
@@ -3600,7 +3600,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AL — Congênita</t>
+          <t>AL — Congenital</t>
         </is>
       </c>
       <c r="B90">
@@ -3634,7 +3634,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B91">
@@ -3671,7 +3671,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B92">
@@ -3708,7 +3708,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B93">
@@ -3745,7 +3745,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B94">
@@ -3782,7 +3782,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B95">
@@ -3816,7 +3816,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B96">
@@ -3853,7 +3853,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B97">
@@ -3890,7 +3890,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B98">
@@ -3927,7 +3927,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B99">
@@ -3964,7 +3964,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B100">
@@ -3998,7 +3998,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BA — Gestacional</t>
+          <t>BA — Gestational</t>
         </is>
       </c>
       <c r="B101">
@@ -4035,7 +4035,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BA — Gestacional</t>
+          <t>BA — Gestational</t>
         </is>
       </c>
       <c r="B102">
@@ -4072,7 +4072,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BA — Gestacional</t>
+          <t>BA — Gestational</t>
         </is>
       </c>
       <c r="B103">
@@ -4106,7 +4106,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BA — Congênita</t>
+          <t>BA — Congenital</t>
         </is>
       </c>
       <c r="B104">
@@ -4143,7 +4143,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BA — Congênita</t>
+          <t>BA — Congenital</t>
         </is>
       </c>
       <c r="B105">
@@ -4180,7 +4180,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BA — Congênita</t>
+          <t>BA — Congenital</t>
         </is>
       </c>
       <c r="B106">
@@ -4214,7 +4214,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B107">
@@ -4251,7 +4251,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B108">
@@ -4288,7 +4288,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B109">
@@ -4325,7 +4325,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B110">
@@ -4359,7 +4359,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B111">
@@ -4396,7 +4396,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B112">
@@ -4433,7 +4433,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B113">
@@ -4470,7 +4470,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B114">
@@ -4504,7 +4504,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B115">
@@ -4541,7 +4541,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B116">
@@ -4578,7 +4578,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B117">
@@ -4615,7 +4615,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B118">
@@ -4649,7 +4649,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B119">
@@ -4686,7 +4686,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B120">
@@ -4723,7 +4723,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B121">
@@ -4760,7 +4760,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B122">
@@ -4797,7 +4797,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B123">
@@ -4831,7 +4831,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RJ — Gestacional</t>
+          <t>RJ — Gestational</t>
         </is>
       </c>
       <c r="B124">
@@ -4868,7 +4868,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RJ — Gestacional</t>
+          <t>RJ — Gestational</t>
         </is>
       </c>
       <c r="B125">
@@ -4905,7 +4905,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RJ — Gestacional</t>
+          <t>RJ — Gestational</t>
         </is>
       </c>
       <c r="B126">
@@ -4939,7 +4939,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B127">
@@ -4976,7 +4976,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B128">
@@ -5013,7 +5013,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B129">
@@ -5050,7 +5050,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B130">
@@ -5084,7 +5084,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SP — Gestacional</t>
+          <t>SP — Gestational</t>
         </is>
       </c>
       <c r="B131">
@@ -5121,7 +5121,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SP — Gestacional</t>
+          <t>SP — Gestational</t>
         </is>
       </c>
       <c r="B132">
@@ -5158,7 +5158,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SP — Gestacional</t>
+          <t>SP — Gestational</t>
         </is>
       </c>
       <c r="B133">
@@ -5192,7 +5192,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B134">
@@ -5229,7 +5229,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B135">
@@ -5266,7 +5266,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B136">
@@ -5303,7 +5303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B137">
@@ -5340,7 +5340,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B138">
@@ -5374,7 +5374,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PR — Gestacional</t>
+          <t>PR — Gestational</t>
         </is>
       </c>
       <c r="B139">
@@ -5411,7 +5411,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PR — Gestacional</t>
+          <t>PR — Gestational</t>
         </is>
       </c>
       <c r="B140">
@@ -5448,7 +5448,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PR — Gestacional</t>
+          <t>PR — Gestational</t>
         </is>
       </c>
       <c r="B141">
@@ -5482,7 +5482,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B142">
@@ -5519,7 +5519,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B143">
@@ -5556,7 +5556,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B144">
@@ -5593,7 +5593,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B145">
@@ -5627,7 +5627,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B146">
@@ -5664,7 +5664,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B147">
@@ -5701,7 +5701,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B148">
@@ -5738,7 +5738,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B149">
@@ -5775,7 +5775,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B150">
@@ -5809,7 +5809,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SC — Congênita</t>
+          <t>SC — Congenital</t>
         </is>
       </c>
       <c r="B151">
@@ -5846,7 +5846,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SC — Congênita</t>
+          <t>SC — Congenital</t>
         </is>
       </c>
       <c r="B152">
@@ -5883,7 +5883,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SC — Congênita</t>
+          <t>SC — Congenital</t>
         </is>
       </c>
       <c r="B153">
@@ -5917,7 +5917,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B154">
@@ -5954,7 +5954,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B155">
@@ -5991,7 +5991,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B156">
@@ -6028,7 +6028,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B157">
@@ -6062,7 +6062,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RS — Congênita</t>
+          <t>RS — Congenital</t>
         </is>
       </c>
       <c r="B158">
@@ -6099,7 +6099,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RS — Congênita</t>
+          <t>RS — Congenital</t>
         </is>
       </c>
       <c r="B159">
@@ -6133,7 +6133,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B160">
@@ -6170,7 +6170,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B161">
@@ -6207,7 +6207,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B162">
@@ -6244,7 +6244,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B163">
@@ -6278,7 +6278,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B164">
@@ -6315,7 +6315,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B165">
@@ -6352,7 +6352,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B166">
@@ -6389,7 +6389,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B167">
@@ -6426,7 +6426,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B168">
@@ -6460,7 +6460,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B169">
@@ -6497,7 +6497,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B170">
@@ -6534,7 +6534,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B171">
@@ -6571,7 +6571,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B172">
@@ -6608,7 +6608,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B173">
@@ -6642,7 +6642,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B174">
@@ -6679,7 +6679,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B175">
@@ -6716,7 +6716,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B176">
@@ -6753,7 +6753,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B177">
@@ -6790,7 +6790,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B178">
@@ -6824,7 +6824,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GO — Gestacional</t>
+          <t>GO — Gestational</t>
         </is>
       </c>
       <c r="B179">
@@ -6861,7 +6861,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GO — Gestacional</t>
+          <t>GO — Gestational</t>
         </is>
       </c>
       <c r="B180">
@@ -6895,7 +6895,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GO — Congênita</t>
+          <t>GO — Congenital</t>
         </is>
       </c>
       <c r="B181">
@@ -6932,7 +6932,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GO — Congênita</t>
+          <t>GO — Congenital</t>
         </is>
       </c>
       <c r="B182">
@@ -6969,7 +6969,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GO — Congênita</t>
+          <t>GO — Congenital</t>
         </is>
       </c>
       <c r="B183">
@@ -7003,7 +7003,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DF — Gestacional</t>
+          <t>DF — Gestational</t>
         </is>
       </c>
       <c r="B184">
@@ -7040,7 +7040,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DF — Gestacional</t>
+          <t>DF — Gestational</t>
         </is>
       </c>
       <c r="B185">
@@ -7077,7 +7077,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DF — Gestacional</t>
+          <t>DF — Gestational</t>
         </is>
       </c>
       <c r="B186">
@@ -7111,7 +7111,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DF — Congênita</t>
+          <t>DF — Congenital</t>
         </is>
       </c>
       <c r="B187">
@@ -7148,7 +7148,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DF — Congênita</t>
+          <t>DF — Congenital</t>
         </is>
       </c>
       <c r="B188">
@@ -7185,7 +7185,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DF — Congênita</t>
+          <t>DF — Congenital</t>
         </is>
       </c>
       <c r="B189">
